--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.86388</v>
+        <v>16.88844</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62553</v>
+        <v>16.44913</v>
       </c>
       <c r="E2" t="n">
-        <v>16.48973</v>
+        <v>16.80005</v>
       </c>
       <c r="F2" t="n">
-        <v>42.89839</v>
+        <v>41.53955</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05108</v>
+        <v>0.05011</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81897</v>
+        <v>1.81678</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.1065</v>
+        <v>16.94682</v>
       </c>
       <c r="D3" t="n">
-        <v>16.40978</v>
+        <v>16.37204</v>
       </c>
       <c r="E3" t="n">
-        <v>16.55862</v>
+        <v>16.69886</v>
       </c>
       <c r="F3" t="n">
-        <v>43.13877</v>
+        <v>42.45305</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05148</v>
+        <v>0.04943</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85082</v>
+        <v>1.81598</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.83769</v>
+        <v>17.27672</v>
       </c>
       <c r="D4" t="n">
-        <v>16.60791</v>
+        <v>16.46969</v>
       </c>
       <c r="E4" t="n">
-        <v>16.6889</v>
+        <v>16.90226</v>
       </c>
       <c r="F4" t="n">
-        <v>42.89445</v>
+        <v>42.69293</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05086</v>
+        <v>0.05147</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82809</v>
+        <v>1.80392</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.61639</v>
+        <v>16.38982</v>
       </c>
       <c r="D6" t="n">
-        <v>15.9468</v>
+        <v>16.04133</v>
       </c>
       <c r="E6" t="n">
-        <v>16.39767</v>
+        <v>16.2642</v>
       </c>
       <c r="F6" t="n">
-        <v>21.62595</v>
+        <v>22.04009</v>
       </c>
       <c r="G6" t="n">
-        <v>34.17308</v>
+        <v>34.80195</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.86169</v>
+        <v>16.82901</v>
       </c>
       <c r="D7" t="n">
-        <v>16.13735</v>
+        <v>15.64228</v>
       </c>
       <c r="E7" t="n">
-        <v>16.42233</v>
+        <v>16.4565</v>
       </c>
       <c r="F7" t="n">
-        <v>21.37208</v>
+        <v>21.12726</v>
       </c>
       <c r="G7" t="n">
-        <v>34.58486</v>
+        <v>34.82122</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.10125</v>
+        <v>16.65263</v>
       </c>
       <c r="D8" t="n">
-        <v>15.68682</v>
+        <v>16.22526</v>
       </c>
       <c r="E8" t="n">
-        <v>16.50668</v>
+        <v>16.32868</v>
       </c>
       <c r="F8" t="n">
-        <v>21.84969</v>
+        <v>21.52915</v>
       </c>
       <c r="G8" t="n">
-        <v>34.63406</v>
+        <v>34.80653</v>
       </c>
     </row>
   </sheetData>
